--- a/data/trans_orig/IP16A12_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16A12_2023-Habitat-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1125</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6357</t>
+          <t>6334</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3209</t>
+          <t>3173</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10877</t>
+          <t>11046</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,62%</t>
+          <t>39,21%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5725</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14519</t>
+          <t>14175</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,35%</t>
+          <t>25,72%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20581</t>
+          <t>20604</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25850</t>
+          <t>25813</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17290</t>
+          <t>17121</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24958</t>
+          <t>24994</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,38%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40586</t>
+          <t>40930</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49380</t>
+          <t>49801</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,65%</t>
+          <t>74,28%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>90,37%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3448</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12269</t>
+          <t>12081</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9446</t>
+          <t>9693</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20794</t>
+          <t>20974</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>15270</t>
+          <t>14489</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29912</t>
+          <t>29547</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,55%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>32513</t>
+          <t>32701</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>41334</t>
+          <t>41367</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>43015</t>
+          <t>42835</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54363</t>
+          <t>54116</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,13%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>78679</t>
+          <t>79044</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>93321</t>
+          <t>94102</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,45%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,66%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2134</t>
+          <t>2292</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15104</t>
+          <t>15778</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>19,6%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2309</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10278</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6312</t>
+          <t>6106</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21031</t>
+          <t>21551</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61967</t>
+          <t>61293</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>74937</t>
+          <t>74779</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,4%</t>
+          <t>79,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46645</t>
+          <t>46769</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54614</t>
+          <t>54547</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112963</t>
+          <t>112443</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>127682</t>
+          <t>127888</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>95,44%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4245</t>
+          <t>4291</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12105</t>
+          <t>12660</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6741</t>
+          <t>6636</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15622</t>
+          <t>15968</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>46,21%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12502</t>
+          <t>12246</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25097</t>
+          <t>25053</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,42%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>38,92%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18456</t>
+          <t>17901</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26316</t>
+          <t>26270</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,39%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>85,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18187</t>
+          <t>17841</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27068</t>
+          <t>27173</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39273</t>
+          <t>39317</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>51868</t>
+          <t>52124</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,58%</t>
+          <t>80,98%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14685</t>
+          <t>15258</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35344</t>
+          <t>35624</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>28349</t>
+          <t>27471</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>47133</t>
+          <t>46478</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>46438</t>
+          <t>45122</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75764</t>
+          <t>75508</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,86%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>144008</t>
+          <t>143728</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>164667</t>
+          <t>164094</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,29%</t>
+          <t>80,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>135576</t>
+          <t>136231</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>154360</t>
+          <t>155238</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,48%</t>
+          <t>84,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>286297</t>
+          <t>286553</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>315623</t>
+          <t>316939</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,17%</t>
+          <t>87,54%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP16A12_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP16A12_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>5799</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2598</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>9986</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>23,06%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>10,33%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>39,71%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>3022</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1125</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6334</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,22%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>4,18%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>23,51%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3173</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11046</t>
+          <t>6503</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,21%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9314</t>
+          <t>9034</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>5529</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14175</t>
+          <t>14100</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>17,2%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>26,84%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>19349</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>15162</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22550</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>76,94%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>60,29%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>89,67%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>23916</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>20604</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>25813</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>88,78%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>76,49%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>95,82%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>21876</t>
+          <t>24147</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>17121</t>
+          <t>20879</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>24994</t>
+          <t>26133</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,79%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>45791</t>
+          <t>43496</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>40930</t>
+          <t>38430</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>49801</t>
+          <t>47001</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>83,1%</t>
+          <t>82,8%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>74,28%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,37%</t>
+          <t>89,48%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>25148</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>25148</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>25148</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>26938</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>26938</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>26938</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>28167</t>
+          <t>27382</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>28167</t>
+          <t>27382</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>28167</t>
+          <t>27382</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>55105</t>
+          <t>52530</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>55105</t>
+          <t>52530</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>55105</t>
+          <t>52530</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,72 +1063,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>13285</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>8328</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>19371</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>23,53%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>14,75%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>34,31%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>7029</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>3415</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>12081</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>15,7%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>7,63%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>26,98%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>14720</t>
+          <t>5425</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9693</t>
+          <t>3030</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>20974</t>
+          <t>9475</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>25,81%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>21749</t>
+          <t>18709</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>14489</t>
+          <t>13174</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>29547</t>
+          <t>25686</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>43173</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>37087</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>48130</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>76,47%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>65,69%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>85,25%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>37753</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>32701</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>41367</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>84,3%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>73,02%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>92,37%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>49089</t>
+          <t>31285</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>42835</t>
+          <t>27235</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>54116</t>
+          <t>33680</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>76,93%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,13%</t>
+          <t>74,19%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>86842</t>
+          <t>74459</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>79044</t>
+          <t>67482</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>94102</t>
+          <t>79994</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>79,97%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>85,86%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>56458</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>44782</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>44782</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>44782</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36710</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36710</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>63809</t>
+          <t>36710</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>108591</t>
+          <t>93168</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>108591</t>
+          <t>93168</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>108591</t>
+          <t>93168</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>4260</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>1860</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>8538</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>8,14%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>16,31%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8157</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2292</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>15778</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>10,58%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>20,47%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4916</t>
+          <t>8080</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>4290</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>10154</t>
+          <t>13555</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>26,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>13073</t>
+          <t>12340</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6106</t>
+          <t>7476</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>21551</t>
+          <t>19124</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>48095</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>43817</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>50495</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>91,86%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>83,69%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>96,45%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>59</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>68914</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>61293</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>74779</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>89,42%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>79,53%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,03%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>52007</t>
+          <t>42746</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>46769</t>
+          <t>37271</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>54547</t>
+          <t>46536</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>91,56%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>120921</t>
+          <t>90841</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>112443</t>
+          <t>84057</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>127888</t>
+          <t>95705</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,92%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>92,75%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>52355</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>77071</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>56923</t>
+          <t>50826</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>133994</t>
+          <t>103181</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>10209</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>6061</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>14765</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>32,39%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>19,23%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>46,85%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>7461</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>4291</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>12660</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>24,41%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>14,04%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>41,42%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>10807</t>
+          <t>7218</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>3827</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>15968</t>
+          <t>11816</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,23%</t>
+          <t>39,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>18268</t>
+          <t>17426</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12246</t>
+          <t>11942</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>25053</t>
+          <t>24061</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,46%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>39,29%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>21308</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>16752</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>25456</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>67,61%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>53,15%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>80,77%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>23100</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>17901</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>26270</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>75,59%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>58,58%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>85,96%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>23002</t>
+          <t>22505</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>17841</t>
+          <t>17907</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27173</t>
+          <t>25896</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,77%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>80,37%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>46102</t>
+          <t>43814</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39317</t>
+          <t>37179</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>52124</t>
+          <t>49298</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>71,62%</t>
+          <t>71,54%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,98%</t>
+          <t>80,5%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>31517</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>30561</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33809</t>
+          <t>29723</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>64370</t>
+          <t>61240</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>33552</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>25608</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>42931</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>20,28%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>15,48%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>25,94%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>43</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>25669</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>15258</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>35624</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>14,31%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>8,51%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>19,86%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>36735</t>
+          <t>23957</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27471</t>
+          <t>17446</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>46478</t>
+          <t>31555</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>20,11%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>62404</t>
+          <t>57510</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>45122</t>
+          <t>47256</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>75508</t>
+          <t>69490</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>22,41%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>131927</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>122548</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>139871</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>79,72%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>74,06%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>84,52%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>186</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>153683</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>143728</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>164094</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>85,69%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>80,14%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>91,49%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>145974</t>
+          <t>120684</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>136231</t>
+          <t>113086</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>155238</t>
+          <t>127195</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>79,89%</t>
+          <t>83,44%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>84,96%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>299657</t>
+          <t>252610</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>286553</t>
+          <t>240630</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>316939</t>
+          <t>262864</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>82,76%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>77,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>84,76%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>165479</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>165479</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>165479</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>229</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>179352</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>179352</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>179352</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>182709</t>
+          <t>144641</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>182709</t>
+          <t>144641</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>182709</t>
+          <t>144641</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>362061</t>
+          <t>310120</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>362061</t>
+          <t>310120</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>362061</t>
+          <t>310120</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
